--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/feb-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/feb-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>28138.41</v>
+        <v>28255.43</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>7726.04</v>
+        <v>7698.53</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2320.13</v>
+        <v>2311.87</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1160.07</v>
+        <v>1155.94</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>46402.64</v>
+        <v>46237.43</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>490.01</v>
+        <v>488.27</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>32608.91</v>
+        <v>32492.81</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>7480.2</v>
+        <v>7453.57</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>4410.11</v>
+        <v>4377.1</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1298.23</v>
+        <v>1288.51</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1160.07</v>
+        <v>1151.38</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2204.12</v>
+        <v>2187.63</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1388.6</v>
+        <v>1378.21</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>11600.66</v>
+        <v>11513.84</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>9999.450000000001</v>
+        <v>9924.620000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1740.1</v>
+        <v>1727.08</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>5561.3</v>
+        <v>5519.68</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>11119.59</v>
+        <v>11036.37</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>8856.17</v>
+        <v>8789.9</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>3480.2</v>
+        <v>3454.15</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>320.7</v>
+        <v>318.3</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1470.41</v>
+        <v>1474.67</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>8124.4</v>
+        <v>8147.93</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>8344.82</v>
+        <v>8368.99</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>8183.48</v>
+        <v>8207.18</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>28095.1</v>
+        <v>28176.49</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>25134.96</v>
+        <v>25207.78</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>126737.2</v>
+        <v>127104.35</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>26846.77</v>
+        <v>26924.54</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2542.86</v>
+        <v>2550.23</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1357.74</v>
+        <v>1361.67</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>432.78</v>
+        <v>434.03</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2412.12</v>
+        <v>2419.11</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>61870.94</v>
+        <v>62050.17</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1160.07</v>
+        <v>1163.43</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>28907.1</v>
+        <v>28990.84</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1394.22</v>
+        <v>1401.43</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>7584.39</v>
+        <v>7623.57</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>19286.09</v>
+        <v>19385.72</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>66777.83</v>
+        <v>67122.78</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>61381.82</v>
+        <v>61698.9</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>3317.79</v>
+        <v>3334.93</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>9835.91</v>
+        <v>9886.719999999999</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>4332.89</v>
+        <v>4355.28</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>23082.7</v>
+        <v>23201.94</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>8864.99</v>
+        <v>8910.790000000001</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>426.5</v>
+        <v>428.7</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>8766.91</v>
+        <v>8812.190000000001</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1005.63</v>
+        <v>1010.83</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>80044.55</v>
+        <v>79707.05</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>13172.4</v>
+        <v>13116.86</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>4640.26</v>
+        <v>4620.7</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>9187.719999999999</v>
+        <v>9148.98</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>29001.65</v>
+        <v>28879.37</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>31713.01</v>
+        <v>31579.3</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1512.03</v>
+        <v>1505.65</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>21548.08</v>
+        <v>21457.22</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>15080.86</v>
+        <v>15017.27</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>707.52</v>
+        <v>704.54</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>706.42</v>
+        <v>703.4400000000001</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>13236.51</v>
+        <v>13180.7</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>870.05</v>
+        <v>866.38</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>30664.89</v>
+        <v>30749.08</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>17972.44</v>
+        <v>18021.78</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>10923.18</v>
+        <v>10953.17</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>23201.32</v>
+        <v>23265.02</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>551.03</v>
+        <v>552.54</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>40585.44</v>
+        <v>40696.86</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>13114.54</v>
+        <v>13150.55</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>25222.36</v>
+        <v>25291.6</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2320.13</v>
+        <v>2326.5</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>17043.18</v>
+        <v>17198.2</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>11323.87</v>
+        <v>11426.87</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>2384.51</v>
+        <v>2406.2</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>1186.92</v>
+        <v>1197.72</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>696.04</v>
+        <v>702.37</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>12107.26</v>
+        <v>12217.38</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>17043.66</v>
+        <v>17198.69</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>23143.31</v>
+        <v>23353.82</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>2784.9</v>
+        <v>2810.23</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>2784.9</v>
+        <v>2810.23</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>43339.16</v>
+        <v>43733.36</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>6584.53</v>
+        <v>6644.42</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>15363.91</v>
+        <v>15503.66</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>14277.22</v>
+        <v>14407.08</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>19761.08</v>
+        <v>19898.66</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>401.96</v>
+        <v>404.76</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>4176.24</v>
+        <v>4205.31</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>9152.969999999999</v>
+        <v>9216.700000000001</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>464.03</v>
+        <v>467.26</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>15695.69</v>
+        <v>15804.97</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>1740.1</v>
+        <v>1751.56</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>15281.56</v>
+        <v>15382.2</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>26797.52</v>
+        <v>26974.01</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>7656.43</v>
+        <v>7706.86</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>76859.58</v>
+        <v>77365.77</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>1092.78</v>
+        <v>1099.98</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>26449.41</v>
+        <v>26623.61</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>9595.540000000001</v>
+        <v>9658.74</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>5512.43</v>
+        <v>5548.74</v>
       </c>
     </row>
     <row r="102">
@@ -6673,7 +6673,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1267371.99</v>
+        <v>1275718.72</v>
       </c>
     </row>
     <row r="103">
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>27502.44</v>
+        <v>27683.57</v>
       </c>
     </row>
     <row r="104">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>29973.9</v>
+        <v>30171.3</v>
       </c>
     </row>
     <row r="105">
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>12508.78</v>
+        <v>12620.2</v>
       </c>
     </row>
     <row r="106">
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>11681.86</v>
+        <v>11785.91</v>
       </c>
     </row>
     <row r="107">
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>11617.94</v>
+        <v>11721.42</v>
       </c>
     </row>
     <row r="108">
@@ -7039,7 +7039,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>14157.1</v>
+        <v>14283.19</v>
       </c>
     </row>
     <row r="109">
@@ -7100,7 +7100,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>1737.78</v>
+        <v>1753.26</v>
       </c>
     </row>
     <row r="110">
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>37113.61</v>
+        <v>37444.17</v>
       </c>
     </row>
     <row r="111">
@@ -7222,7 +7222,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>19203.44</v>
+        <v>19374.48</v>
       </c>
     </row>
     <row r="112">
@@ -7283,7 +7283,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>1160.07</v>
+        <v>1170.4</v>
       </c>
     </row>
     <row r="113">
@@ -7344,7 +7344,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>1064.94</v>
+        <v>1074.43</v>
       </c>
     </row>
     <row r="114">
@@ -7405,7 +7405,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>1429</v>
+        <v>1426.55</v>
       </c>
     </row>
     <row r="115">
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>9515.209999999999</v>
+        <v>9498.9</v>
       </c>
     </row>
     <row r="116">
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>8761.4</v>
+        <v>8746.379999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>12658.64</v>
+        <v>12636.94</v>
       </c>
     </row>
     <row r="118">
@@ -7649,7 +7649,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>104.7</v>
+        <v>104.52</v>
       </c>
     </row>
     <row r="119">
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>6324.47</v>
+        <v>6313.63</v>
       </c>
     </row>
     <row r="120">
@@ -7775,7 +7775,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>25465.36</v>
+        <v>25421.71</v>
       </c>
     </row>
     <row r="121">
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>17400.99</v>
+        <v>17371.16</v>
       </c>
     </row>
     <row r="122">
@@ -7897,7 +7897,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>3676.48</v>
+        <v>3670.18</v>
       </c>
     </row>
     <row r="123">
@@ -7958,7 +7958,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>30479.74</v>
+        <v>30448.31</v>
       </c>
     </row>
     <row r="124">
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>46.29</v>
+        <v>46.24</v>
       </c>
     </row>
     <row r="125">
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>6855.93</v>
+        <v>6848.86</v>
       </c>
     </row>
     <row r="126">
@@ -8141,7 +8141,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>1738.99</v>
+        <v>1737.2</v>
       </c>
     </row>
     <row r="127">
@@ -8202,7 +8202,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>16874.78</v>
+        <v>16857.38</v>
       </c>
     </row>
     <row r="128">
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>3735.41</v>
+        <v>3731.56</v>
       </c>
     </row>
     <row r="129">
@@ -8324,7 +8324,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>3747.13</v>
+        <v>3743.27</v>
       </c>
     </row>
     <row r="130">
@@ -8385,7 +8385,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>16913.36</v>
+        <v>16895.91</v>
       </c>
     </row>
     <row r="131">
@@ -8446,7 +8446,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>346.05</v>
+        <v>345.69</v>
       </c>
     </row>
     <row r="132">
@@ -8507,7 +8507,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>24995.44</v>
+        <v>24969.66</v>
       </c>
     </row>
     <row r="133">
@@ -8568,7 +8568,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>191412.19</v>
+        <v>190040.92</v>
       </c>
     </row>
     <row r="134">
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>70710.53999999999</v>
+        <v>70203.98</v>
       </c>
     </row>
     <row r="135">
@@ -8690,7 +8690,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>525.89</v>
+        <v>522.13</v>
       </c>
     </row>
     <row r="136">
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>2884.38</v>
+        <v>2863.72</v>
       </c>
     </row>
     <row r="137">
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>1747.63</v>
+        <v>1735.11</v>
       </c>
     </row>
     <row r="138">
@@ -8873,7 +8873,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>11172.71</v>
+        <v>11092.67</v>
       </c>
     </row>
     <row r="139">
@@ -8934,7 +8934,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>1160.07</v>
+        <v>1151.75</v>
       </c>
     </row>
     <row r="140">
@@ -8995,7 +8995,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1160.07</v>
+        <v>1151.75</v>
       </c>
     </row>
     <row r="141">
@@ -9056,7 +9056,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>4640.26</v>
+        <v>4607.02</v>
       </c>
     </row>
     <row r="142">
@@ -9117,7 +9117,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>19475.1</v>
+        <v>19335.58</v>
       </c>
     </row>
     <row r="143">
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>5842.03</v>
+        <v>5833.44</v>
       </c>
     </row>
     <row r="144">
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>110797.1</v>
+        <v>110634.11</v>
       </c>
     </row>
     <row r="145">
@@ -9304,7 +9304,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>2320.13</v>
+        <v>2316.72</v>
       </c>
     </row>
     <row r="146">
@@ -9365,7 +9365,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>12960.26</v>
+        <v>12941.19</v>
       </c>
     </row>
     <row r="147">
@@ -9426,7 +9426,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>13968.42</v>
+        <v>13947.87</v>
       </c>
     </row>
     <row r="148">
@@ -9487,7 +9487,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>9310.219999999999</v>
+        <v>9259.52</v>
       </c>
     </row>
     <row r="149">
@@ -9548,7 +9548,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>903.6900000000001</v>
+        <v>898.77</v>
       </c>
     </row>
     <row r="150">
@@ -9609,7 +9609,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>23201.32</v>
+        <v>23074.97</v>
       </c>
     </row>
     <row r="151">
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>16239.74</v>
+        <v>16151.3</v>
       </c>
     </row>
     <row r="152">
@@ -9731,7 +9731,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>997.5</v>
+        <v>992.0700000000001</v>
       </c>
     </row>
     <row r="153">
@@ -9792,7 +9792,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>17439.97</v>
+        <v>17344.99</v>
       </c>
     </row>
     <row r="154">
@@ -9853,7 +9853,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>6819.56</v>
+        <v>6779.38</v>
       </c>
     </row>
     <row r="155">
@@ -9914,7 +9914,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>232.01</v>
+        <v>230.65</v>
       </c>
     </row>
     <row r="156">
@@ -9975,7 +9975,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>37459.28</v>
+        <v>37238.53</v>
       </c>
     </row>
     <row r="157">
@@ -10036,7 +10036,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>1416.37</v>
+        <v>1408.02</v>
       </c>
     </row>
     <row r="158">
@@ -10097,7 +10097,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>75404.28</v>
+        <v>74959.92999999999</v>
       </c>
     </row>
     <row r="159">
@@ -10158,7 +10158,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>41208.32</v>
+        <v>40965.48</v>
       </c>
     </row>
     <row r="160">
@@ -10219,7 +10219,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>15662.51</v>
+        <v>15570.21</v>
       </c>
     </row>
     <row r="161">
@@ -10280,7 +10280,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>10257.88</v>
+        <v>10197.43</v>
       </c>
     </row>
     <row r="162">
@@ -10341,7 +10341,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>7430.92</v>
+        <v>7387.13</v>
       </c>
     </row>
     <row r="163">
@@ -10402,7 +10402,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>7685.68</v>
+        <v>7640.39</v>
       </c>
     </row>
     <row r="164">
@@ -10463,7 +10463,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>19721.12</v>
+        <v>19601.29</v>
       </c>
     </row>
     <row r="165">
@@ -10524,7 +10524,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>18360.36</v>
+        <v>18248.8</v>
       </c>
     </row>
     <row r="166">
@@ -10585,7 +10585,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>40580.15</v>
+        <v>40333.57</v>
       </c>
     </row>
     <row r="167">
@@ -10646,7 +10646,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>410.66</v>
+        <v>408.17</v>
       </c>
     </row>
     <row r="168">
@@ -10707,7 +10707,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>1071.9</v>
+        <v>1065.39</v>
       </c>
     </row>
     <row r="169">
@@ -10768,7 +10768,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>174.01</v>
+        <v>172.95</v>
       </c>
     </row>
     <row r="170">
@@ -10829,7 +10829,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>11728.47</v>
+        <v>11657.21</v>
       </c>
     </row>
     <row r="171">
@@ -10890,7 +10890,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>3658.85</v>
+        <v>3636.61</v>
       </c>
     </row>
     <row r="172">
@@ -10951,7 +10951,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>13597.83</v>
+        <v>13515.2</v>
       </c>
     </row>
     <row r="173">
@@ -11012,7 +11012,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>671.71</v>
+        <v>669.11</v>
       </c>
     </row>
     <row r="174">
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>54523.1</v>
+        <v>54312.66</v>
       </c>
     </row>
     <row r="175">
@@ -11134,7 +11134,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>35857.15</v>
+        <v>35718.75</v>
       </c>
     </row>
     <row r="176">
@@ -11195,7 +11195,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>10112.53</v>
+        <v>10073.49</v>
       </c>
     </row>
     <row r="177">
@@ -11256,7 +11256,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>15539.08</v>
+        <v>15479.11</v>
       </c>
     </row>
     <row r="178">
@@ -11317,7 +11317,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>5078.3</v>
+        <v>5058.7</v>
       </c>
     </row>
     <row r="179">
@@ -11378,7 +11378,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>13920.79</v>
+        <v>13867.06</v>
       </c>
     </row>
     <row r="180">
@@ -11439,7 +11439,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>8153.39</v>
+        <v>8121.92</v>
       </c>
     </row>
     <row r="181">
@@ -11500,7 +11500,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>6381.29</v>
+        <v>6356.66</v>
       </c>
     </row>
     <row r="182">
@@ -11565,7 +11565,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>548029.28</v>
+        <v>545914.0699999999</v>
       </c>
     </row>
     <row r="183">
@@ -11626,7 +11626,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>23201.32</v>
+        <v>23111.77</v>
       </c>
     </row>
     <row r="184">
@@ -11687,7 +11687,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>1566.09</v>
+        <v>1560.04</v>
       </c>
     </row>
     <row r="185">
@@ -11748,7 +11748,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>20884.38</v>
+        <v>20803.77</v>
       </c>
     </row>
     <row r="186">
@@ -11809,7 +11809,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>13341.3</v>
+        <v>13289.8</v>
       </c>
     </row>
     <row r="187">
@@ -11870,7 +11870,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>34825.18</v>
+        <v>34690.76</v>
       </c>
     </row>
     <row r="188">
@@ -11931,7 +11931,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>10237.61</v>
+        <v>10198.1</v>
       </c>
     </row>
     <row r="189">
@@ -11992,7 +11992,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>33484.14</v>
+        <v>33354.9</v>
       </c>
     </row>
     <row r="190">
@@ -12053,7 +12053,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>497.03</v>
+        <v>495.11</v>
       </c>
     </row>
     <row r="191">
@@ -12114,7 +12114,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>30540.25</v>
+        <v>30422.37</v>
       </c>
     </row>
     <row r="192">
@@ -12175,7 +12175,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>9835.91</v>
+        <v>9797.950000000001</v>
       </c>
     </row>
     <row r="193">
@@ -12236,7 +12236,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>21148.58</v>
+        <v>21066.95</v>
       </c>
     </row>
     <row r="194">
@@ -12297,7 +12297,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>52534.61</v>
+        <v>52806.6</v>
       </c>
     </row>
     <row r="195">
@@ -12358,7 +12358,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>19837.13</v>
+        <v>19939.83</v>
       </c>
     </row>
     <row r="196">
@@ -12419,7 +12419,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>48209.12</v>
+        <v>48458.71</v>
       </c>
     </row>
     <row r="197">
@@ -12480,7 +12480,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>61658.5</v>
+        <v>61977.73</v>
       </c>
     </row>
     <row r="198">
@@ -12541,7 +12541,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>2320.13</v>
+        <v>2332.14</v>
       </c>
     </row>
     <row r="199">
@@ -12602,7 +12602,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>42109.26</v>
+        <v>42327.27</v>
       </c>
     </row>
     <row r="200">
@@ -12663,7 +12663,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>13114.54</v>
+        <v>13182.44</v>
       </c>
     </row>
     <row r="201">
@@ -12728,7 +12728,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>242167.23</v>
+        <v>243421.02</v>
       </c>
     </row>
     <row r="202">
@@ -12789,7 +12789,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>6166</v>
+        <v>6197.92</v>
       </c>
     </row>
     <row r="203">
@@ -12850,7 +12850,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>37209.6</v>
+        <v>37402.25</v>
       </c>
     </row>
     <row r="204">
@@ -12911,7 +12911,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>2192.5</v>
+        <v>2203.85</v>
       </c>
     </row>
     <row r="205">
@@ -12972,7 +12972,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>6146.03</v>
+        <v>6177.85</v>
       </c>
     </row>
     <row r="206">
@@ -13037,7 +13037,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>302961.85</v>
+        <v>304530.39</v>
       </c>
     </row>
     <row r="207">
@@ -13098,7 +13098,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>60613.44</v>
+        <v>60927.26</v>
       </c>
     </row>
     <row r="208">
@@ -13159,7 +13159,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>50380.79</v>
+        <v>50429.35</v>
       </c>
     </row>
     <row r="209">
@@ -13220,7 +13220,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>9280.530000000001</v>
+        <v>9289.469999999999</v>
       </c>
     </row>
     <row r="210">
@@ -13281,7 +13281,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>32786.36</v>
+        <v>32817.96</v>
       </c>
     </row>
     <row r="211">
@@ -13342,7 +13342,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>34827.38</v>
+        <v>34860.95</v>
       </c>
     </row>
     <row r="212">
@@ -13403,7 +13403,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>1482.49</v>
+        <v>1483.92</v>
       </c>
     </row>
     <row r="213">
@@ -13464,7 +13464,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>4924.57</v>
+        <v>4929.31</v>
       </c>
     </row>
     <row r="214">
@@ -13525,7 +13525,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>1361.05</v>
+        <v>1362.36</v>
       </c>
     </row>
     <row r="215">
@@ -13586,7 +13586,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>385.72</v>
+        <v>386.09</v>
       </c>
     </row>
     <row r="216">
@@ -13647,7 +13647,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>3857.22</v>
+        <v>3860.94</v>
       </c>
     </row>
     <row r="217">
@@ -13708,7 +13708,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>25639.49</v>
+        <v>25664.2</v>
       </c>
     </row>
     <row r="218">
@@ -13769,7 +13769,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>36669.63</v>
+        <v>36704.97</v>
       </c>
     </row>
     <row r="219">
@@ -13830,7 +13830,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>7337.09</v>
+        <v>7344.16</v>
       </c>
     </row>
     <row r="220">
@@ -13891,7 +13891,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>19867.29</v>
+        <v>19886.44</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/feb-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/feb-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC feb-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC feb-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7705,7 +7705,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9650,7 +9650,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10565,7 +10565,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -11053,7 +11053,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11358,7 +11358,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11556,7 +11556,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -12155,7 +12155,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12277,7 +12277,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12643,7 +12643,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12719,7 +12719,7 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -12769,7 +12769,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12891,7 +12891,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">

--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/feb-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/feb-2026.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Yumbel - Depto. Educacion</t>
+          <t>I MUNICIPALIDAD DE YUMBEL</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Yumbel - Depto. Educacion</t>
+          <t>I MUNICIPALIDAD DE YUMBEL</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>REGIMIENTO 12 "SANGRA"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dirección de Planificación de Inf. del Ejército</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE LOS SERVICIOS DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE FINANZAS DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SEREMI Bienes Nacionales Región Metropolitana</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Escuela de Gendarmeria</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Quillon - Educación</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Servicio de Salud Atacama</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Valparaíso</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hospital de Achao</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>DIRECCION DE SEGURIDAD Y OPERACIONES MARITIMAS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>DIRECCION DE SEGURIDAD Y OPERACIONES MARITIMAS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>BASE NAVAL PUERTO MONTT</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>REGIMIENTO 12 "SANGRA"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7750,7 +7750,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hospital de Queilen</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7872,7 +7872,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8055,7 +8055,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8299,7 +8299,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>DIRECCION DE SEGURIDAD Y OPERACIONES MARITIMAS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8665,7 +8665,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8909,7 +8909,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>REGIMIENTO 12 "SANGRA"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9706,7 +9706,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>ESTACION NAVAL METROPOLITANA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -10072,7 +10072,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10377,7 +10377,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>DIRECCION DE SEGURIDAD Y OPERACIONES MARITIMAS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10743,7 +10743,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DEL TERRITORIO MARIT Y MM (AB)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10987,7 +10987,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Comité de Seguro Agricola</t>
+          <t>Comité de Seguros del Agro</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11170,7 +11170,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11662,7 +11662,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11850,7 +11850,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11906,7 +11906,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Consultorio General Urbano Victor Domingo Silva</t>
+          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12516,7 +12516,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12577,7 +12577,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -12699,12 +12699,12 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>ESTADO MAYOR CONJUNTO</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12886,7 +12886,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -12947,7 +12947,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13317,7 +13317,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13500,7 +13500,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">

--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/feb-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/feb-2026.xlsx
@@ -562,7 +562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2057,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2122,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2187,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2317,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2382,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2577,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2642,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2707,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2772,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2837,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2902,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2967,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3032,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3097,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3162,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3227,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3292,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3357,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3422,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3487,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3552,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3617,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3682,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3747,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3812,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3877,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3942,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +4007,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4072,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4137,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4202,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4267,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4332,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4397,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4462,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4527,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4592,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4657,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4722,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4787,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4852,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4917,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4982,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +5047,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5112,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5177,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5242,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5307,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5372,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5437,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5502,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5567,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5632,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5697,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5762,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5827,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5892,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5957,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +6022,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6087,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6152,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6217,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6282,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6347,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6412,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6477,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6542,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6607,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6672,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6737,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6802,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6867,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6932,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6997,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6727,7 +7127,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6788,7 +7192,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6849,7 +7257,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6910,7 +7322,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6971,7 +7387,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7032,7 +7452,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7093,7 +7517,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7154,7 +7582,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7215,7 +7647,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7276,7 +7712,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7337,7 +7777,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7398,7 +7842,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7459,7 +7907,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7520,7 +7972,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7581,7 +8037,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7642,7 +8102,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7768,7 +8232,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7829,7 +8297,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7890,7 +8362,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7951,7 +8427,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8012,7 +8492,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8073,7 +8557,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8134,7 +8622,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8195,7 +8687,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8256,7 +8752,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8317,7 +8817,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8378,7 +8882,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8439,7 +8947,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8500,7 +9012,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8561,7 +9077,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8622,7 +9142,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8683,7 +9207,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8744,7 +9272,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8805,7 +9337,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8866,7 +9402,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8927,7 +9467,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8988,7 +9532,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9049,7 +9597,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9110,7 +9662,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9171,7 +9727,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9297,7 +9857,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9358,7 +9922,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9419,7 +9987,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9480,7 +10052,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9541,7 +10117,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9602,7 +10182,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9663,7 +10247,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9724,7 +10312,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9785,7 +10377,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9846,7 +10442,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9907,7 +10507,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9968,7 +10572,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10029,7 +10637,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10090,7 +10702,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10151,7 +10767,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10212,7 +10832,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10273,7 +10897,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10334,7 +10962,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10395,7 +11027,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10456,7 +11092,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10517,7 +11157,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10578,7 +11222,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10639,7 +11287,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10700,7 +11352,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10761,7 +11417,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10822,7 +11482,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10883,7 +11547,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10944,7 +11612,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11005,7 +11677,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11066,7 +11742,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11127,7 +11807,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11188,7 +11872,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11249,7 +11937,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11310,7 +12002,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11371,7 +12067,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11432,7 +12132,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11493,7 +12197,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11619,7 +12327,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11680,7 +12392,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11741,7 +12457,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11802,7 +12522,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11863,7 +12587,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11924,7 +12652,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11985,7 +12717,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12046,7 +12782,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12107,7 +12847,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12168,7 +12912,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12229,7 +12977,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12290,7 +13042,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12351,7 +13107,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12412,7 +13172,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12473,7 +13237,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12534,7 +13302,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12595,7 +13367,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12656,7 +13432,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12782,7 +13562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12843,7 +13627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12904,7 +13692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12965,7 +13757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13091,7 +13887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13152,7 +13952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13213,7 +14017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13274,7 +14082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13335,7 +14147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13396,7 +14212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13457,7 +14277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13518,7 +14342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13579,7 +14407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13640,7 +14472,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13701,7 +14537,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13762,7 +14602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13823,7 +14667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13884,7 +14732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/feb-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/feb-2026.xlsx
@@ -5409,7 +5409,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -7489,7 +7489,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
